--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="134">
   <si>
     <t>2020 May</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Alert</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>8%</t>
@@ -1240,13 +1243,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1467,13 +1470,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1694,13 +1697,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV4" t="s">
         <v>113</v>
       </c>
-      <c r="BV4" t="s">
-        <v>112</v>
-      </c>
       <c r="BW4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1921,13 +1924,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2148,13 +2151,13 @@
         <v>109</v>
       </c>
       <c r="BU6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2333,7 +2336,7 @@
         <v>108</v>
       </c>
       <c r="BG7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH7" t="s">
         <v>108</v>
@@ -2375,13 +2378,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2602,13 +2605,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2829,13 +2832,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3056,13 +3059,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3283,13 +3286,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BW11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3510,13 +3513,13 @@
         <v>109</v>
       </c>
       <c r="BU12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3737,13 +3740,13 @@
         <v>109</v>
       </c>
       <c r="BU13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3964,13 +3967,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4191,13 +4194,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4418,13 +4421,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BW16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4645,13 +4648,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV17" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW17" t="s">
         <v>120</v>
-      </c>
-      <c r="BV17" t="s">
-        <v>129</v>
-      </c>
-      <c r="BW17" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4872,13 +4875,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5099,13 +5102,13 @@
         <v>110</v>
       </c>
       <c r="BU19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5326,13 +5329,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5553,13 +5556,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
+        <v>123</v>
+      </c>
+      <c r="BV21" t="s">
+        <v>113</v>
+      </c>
+      <c r="BW21" t="s">
         <v>122</v>
-      </c>
-      <c r="BV21" t="s">
-        <v>112</v>
-      </c>
-      <c r="BW21" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5780,13 +5783,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -6007,13 +6010,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6234,13 +6237,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BV24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6461,13 +6464,13 @@
         <v>109</v>
       </c>
       <c r="BU25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BV25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6688,13 +6691,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6915,13 +6918,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BV27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7142,13 +7145,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7369,13 +7372,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7596,13 +7599,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7823,13 +7826,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8050,13 +8053,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8277,13 +8280,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BW33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8504,13 +8507,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,79 +343,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>30%</t>
   </si>
 </sst>
 </file>
@@ -1045,10 +976,10 @@
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I2" t="s">
         <v>108</v>
@@ -1144,10 +1075,10 @@
         <v>108</v>
       </c>
       <c r="AN2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
         <v>108</v>
@@ -1213,25 +1144,25 @@
         <v>108</v>
       </c>
       <c r="BK2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BL2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BM2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BN2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR2" t="s">
         <v>108</v>
@@ -1243,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1335,7 +1266,7 @@
         <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="s">
         <v>108</v>
@@ -1359,10 +1290,10 @@
         <v>108</v>
       </c>
       <c r="AJ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL3" t="s">
         <v>108</v>
@@ -1386,10 +1317,10 @@
         <v>108</v>
       </c>
       <c r="AS3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU3" t="s">
         <v>108</v>
@@ -1407,13 +1338,13 @@
         <v>108</v>
       </c>
       <c r="AZ3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC3" t="s">
         <v>108</v>
@@ -1422,10 +1353,10 @@
         <v>108</v>
       </c>
       <c r="BE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG3" t="s">
         <v>108</v>
@@ -1470,13 +1401,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1559,13 +1490,13 @@
         <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
         <v>108</v>
@@ -1697,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1714,13 +1645,13 @@
         <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
         <v>108</v>
@@ -1750,13 +1681,13 @@
         <v>108</v>
       </c>
       <c r="O5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R5" t="s">
         <v>108</v>
@@ -1786,13 +1717,13 @@
         <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD5" t="s">
         <v>108</v>
@@ -1822,13 +1753,13 @@
         <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP5" t="s">
         <v>108</v>
@@ -1858,13 +1789,13 @@
         <v>108</v>
       </c>
       <c r="AY5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB5" t="s">
         <v>108</v>
@@ -1894,13 +1825,13 @@
         <v>108</v>
       </c>
       <c r="BK5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN5" t="s">
         <v>108</v>
@@ -1924,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1950,10 +1881,10 @@
         <v>108</v>
       </c>
       <c r="F6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H6" t="s">
         <v>108</v>
@@ -2079,7 +2010,7 @@
         <v>108</v>
       </c>
       <c r="AW6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX6" t="s">
         <v>108</v>
@@ -2091,7 +2022,7 @@
         <v>108</v>
       </c>
       <c r="BA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB6" t="s">
         <v>108</v>
@@ -2103,19 +2034,19 @@
         <v>108</v>
       </c>
       <c r="BE6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BJ6" t="s">
         <v>108</v>
@@ -2127,7 +2058,7 @@
         <v>108</v>
       </c>
       <c r="BM6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BN6" t="s">
         <v>108</v>
@@ -2139,25 +2070,25 @@
         <v>108</v>
       </c>
       <c r="BQ6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2165,55 +2096,55 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S7" t="s">
         <v>108</v>
@@ -2336,7 +2267,7 @@
         <v>108</v>
       </c>
       <c r="BG7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BH7" t="s">
         <v>108</v>
@@ -2378,13 +2309,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2392,7 +2323,7 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
         <v>108</v>
@@ -2482,37 +2413,37 @@
         <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ8" t="s">
         <v>108</v>
@@ -2605,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2736,28 +2667,28 @@
         <v>108</v>
       </c>
       <c r="AO9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW9" t="s">
         <v>108</v>
@@ -2769,31 +2700,31 @@
         <v>108</v>
       </c>
       <c r="AZ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BI9" t="s">
         <v>108</v>
@@ -2832,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2942,13 +2873,13 @@
         <v>108</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI10" t="s">
         <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s">
         <v>108</v>
@@ -2957,16 +2888,16 @@
         <v>108</v>
       </c>
       <c r="AM10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ10" t="s">
         <v>108</v>
@@ -2978,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="AT10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU10" t="s">
         <v>108</v>
       </c>
       <c r="AV10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW10" t="s">
         <v>108</v>
@@ -2993,16 +2924,16 @@
         <v>108</v>
       </c>
       <c r="AY10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC10" t="s">
         <v>108</v>
@@ -3014,7 +2945,7 @@
         <v>108</v>
       </c>
       <c r="BF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG10" t="s">
         <v>108</v>
@@ -3059,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3184,31 +3115,31 @@
         <v>108</v>
       </c>
       <c r="AM11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO11" t="s">
         <v>108</v>
       </c>
       <c r="AP11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS11" t="s">
         <v>108</v>
       </c>
       <c r="AT11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV11" t="s">
         <v>108</v>
@@ -3223,28 +3154,28 @@
         <v>108</v>
       </c>
       <c r="AZ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH11" t="s">
         <v>108</v>
@@ -3286,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3300,31 +3231,31 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
         <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
         <v>108</v>
@@ -3333,7 +3264,7 @@
         <v>108</v>
       </c>
       <c r="M12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
         <v>108</v>
@@ -3477,49 +3408,49 @@
         <v>108</v>
       </c>
       <c r="BI12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BJ12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BN12" t="s">
         <v>108</v>
       </c>
       <c r="BO12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3608,13 +3539,13 @@
         <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
         <v>108</v>
@@ -3689,7 +3620,7 @@
         <v>108</v>
       </c>
       <c r="BD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE13" t="s">
         <v>108</v>
@@ -3698,34 +3629,34 @@
         <v>108</v>
       </c>
       <c r="BG13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BJ13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BN13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ13" t="s">
         <v>108</v>
@@ -3734,19 +3665,19 @@
         <v>108</v>
       </c>
       <c r="BS13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3967,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4125,7 +4056,7 @@
         <v>108</v>
       </c>
       <c r="AX15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY15" t="s">
         <v>108</v>
@@ -4161,7 +4092,7 @@
         <v>108</v>
       </c>
       <c r="BJ15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK15" t="s">
         <v>108</v>
@@ -4194,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4208,40 +4139,40 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N16" t="s">
         <v>108</v>
@@ -4265,19 +4196,19 @@
         <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z16" t="s">
         <v>108</v>
@@ -4301,19 +4232,19 @@
         <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL16" t="s">
         <v>108</v>
@@ -4337,19 +4268,19 @@
         <v>108</v>
       </c>
       <c r="AS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX16" t="s">
         <v>108</v>
@@ -4373,19 +4304,19 @@
         <v>108</v>
       </c>
       <c r="BE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ16" t="s">
         <v>108</v>
@@ -4409,25 +4340,25 @@
         <v>108</v>
       </c>
       <c r="BQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4453,7 +4384,7 @@
         <v>108</v>
       </c>
       <c r="H17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
         <v>108</v>
@@ -4462,13 +4393,13 @@
         <v>108</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N17" t="s">
         <v>108</v>
@@ -4489,7 +4420,7 @@
         <v>108</v>
       </c>
       <c r="T17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U17" t="s">
         <v>108</v>
@@ -4531,31 +4462,31 @@
         <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
         <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
         <v>108</v>
       </c>
       <c r="AM17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s">
         <v>108</v>
       </c>
       <c r="AO17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
         <v>108</v>
@@ -4648,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4671,28 +4602,28 @@
         <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M18" t="s">
         <v>108</v>
@@ -4707,28 +4638,28 @@
         <v>108</v>
       </c>
       <c r="Q18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y18" t="s">
         <v>108</v>
@@ -4743,28 +4674,28 @@
         <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK18" t="s">
         <v>108</v>
@@ -4779,28 +4710,28 @@
         <v>108</v>
       </c>
       <c r="AO18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW18" t="s">
         <v>108</v>
@@ -4815,28 +4746,28 @@
         <v>108</v>
       </c>
       <c r="BA18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI18" t="s">
         <v>108</v>
@@ -4851,37 +4782,37 @@
         <v>108</v>
       </c>
       <c r="BM18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4967,7 +4898,7 @@
         <v>108</v>
       </c>
       <c r="AB19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC19" t="s">
         <v>108</v>
@@ -5015,31 +4946,31 @@
         <v>108</v>
       </c>
       <c r="AR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
         <v>108</v>
       </c>
       <c r="AZ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA19" t="s">
         <v>108</v>
@@ -5051,31 +4982,31 @@
         <v>108</v>
       </c>
       <c r="BD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BJ19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK19" t="s">
         <v>108</v>
       </c>
       <c r="BL19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BM19" t="s">
         <v>108</v>
@@ -5090,25 +5021,25 @@
         <v>108</v>
       </c>
       <c r="BQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5128,31 +5059,31 @@
         <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s">
         <v>108</v>
@@ -5164,31 +5095,31 @@
         <v>108</v>
       </c>
       <c r="R20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
         <v>108</v>
@@ -5329,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5433,34 +5364,34 @@
         <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP21" t="s">
         <v>108</v>
@@ -5493,10 +5424,10 @@
         <v>108</v>
       </c>
       <c r="AZ21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB21" t="s">
         <v>108</v>
@@ -5505,7 +5436,7 @@
         <v>108</v>
       </c>
       <c r="BD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE21" t="s">
         <v>108</v>
@@ -5517,13 +5448,13 @@
         <v>108</v>
       </c>
       <c r="BH21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BI21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BJ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK21" t="s">
         <v>108</v>
@@ -5556,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5570,226 +5501,226 @@
         <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -6010,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6027,13 +5958,13 @@
         <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>108</v>
@@ -6063,13 +5994,13 @@
         <v>108</v>
       </c>
       <c r="O24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R24" t="s">
         <v>108</v>
@@ -6099,13 +6030,13 @@
         <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD24" t="s">
         <v>108</v>
@@ -6135,16 +6066,16 @@
         <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ24" t="s">
         <v>108</v>
@@ -6171,13 +6102,13 @@
         <v>108</v>
       </c>
       <c r="AY24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB24" t="s">
         <v>108</v>
@@ -6207,13 +6138,13 @@
         <v>108</v>
       </c>
       <c r="BK24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN24" t="s">
         <v>108</v>
@@ -6237,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6392,85 +6323,85 @@
         <v>108</v>
       </c>
       <c r="AW25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BJ25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BN25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6691,13 +6622,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6738,19 +6669,19 @@
         <v>108</v>
       </c>
       <c r="M27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R27" t="s">
         <v>108</v>
@@ -6792,28 +6723,28 @@
         <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
         <v>108</v>
@@ -6918,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7145,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7159,7 +7090,7 @@
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
         <v>108</v>
@@ -7189,10 +7120,10 @@
         <v>108</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
         <v>108</v>
@@ -7225,10 +7156,10 @@
         <v>108</v>
       </c>
       <c r="X29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z29" t="s">
         <v>108</v>
@@ -7285,13 +7216,13 @@
         <v>108</v>
       </c>
       <c r="AR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU29" t="s">
         <v>108</v>
@@ -7372,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7410,13 +7341,13 @@
         <v>108</v>
       </c>
       <c r="J30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s">
         <v>108</v>
@@ -7479,7 +7410,7 @@
         <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
         <v>108</v>
@@ -7494,7 +7425,7 @@
         <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
         <v>108</v>
@@ -7599,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7616,64 +7547,64 @@
         <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W31" t="s">
         <v>108</v>
@@ -7826,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7846,7 +7777,7 @@
         <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>108</v>
@@ -7948,64 +7879,64 @@
         <v>108</v>
       </c>
       <c r="AL32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BD32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF32" t="s">
         <v>108</v>
@@ -8053,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8076,10 +8007,10 @@
         <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G33" t="s">
         <v>108</v>
@@ -8100,22 +8031,22 @@
         <v>108</v>
       </c>
       <c r="M33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P33" t="s">
         <v>108</v>
       </c>
       <c r="Q33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S33" t="s">
         <v>108</v>
@@ -8136,13 +8067,13 @@
         <v>108</v>
       </c>
       <c r="Y33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
         <v>108</v>
@@ -8280,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8363,7 +8294,7 @@
         <v>108</v>
       </c>
       <c r="Y34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z34" t="s">
         <v>108</v>
@@ -8441,28 +8372,28 @@
         <v>108</v>
       </c>
       <c r="AY34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AZ34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BA34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BB34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD34" t="s">
         <v>108</v>
       </c>
       <c r="BE34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG34" t="s">
         <v>108</v>
@@ -8477,28 +8408,28 @@
         <v>108</v>
       </c>
       <c r="BK34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BN34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BP34" t="s">
         <v>108</v>
       </c>
       <c r="BQ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS34" t="s">
         <v>108</v>
@@ -8507,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_percentile_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
